--- a/ניתוח_אימוני_SUP_v5.xlsx
+++ b/ניתוח_אימוני_SUP_v5.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\claude-projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\claude-projects\sup-challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="172">
   <si>
     <t>📊 ניתוח אימוני SUP — לוח מעקב</t>
   </si>
@@ -463,6 +463,15 @@
   </si>
   <si>
     <t>12:40</t>
+  </si>
+  <si>
+    <t>02.05.2026</t>
+  </si>
+  <si>
+    <t>1:27:38</t>
+  </si>
+  <si>
+    <t>1:04:59</t>
   </si>
   <si>
     <t>📅 SUP — סיכום חודשי לפי סוג אימון 📋</t>
@@ -1113,7 +1122,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BE3F-40C6-83AF-1E41318CBFED}"/>
+              <c16:uniqueId val="{00000000-3F16-4720-BF07-106AA207AA2F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1317,7 +1326,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-75B5-468E-A924-EF1B85A07DC7}"/>
+              <c16:uniqueId val="{00000000-BA49-40F1-B892-3B856527F482}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1529,7 +1538,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B7E1-4ED4-B79C-3687971CDA74}"/>
+              <c16:uniqueId val="{00000000-A64B-49B5-A455-4C18718611ED}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1733,7 +1742,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5CC9-456C-91FF-0E4E38955722}"/>
+              <c16:uniqueId val="{00000000-CA20-4B61-A3D6-9044443CFFC6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2087,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="39" customWidth="1"/>
@@ -3405,6 +3414,44 @@
         <v>144</v>
       </c>
       <c r="L35" s="28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="28">
+        <v>11.17</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="F36" s="28">
+        <v>7.6</v>
+      </c>
+      <c r="G36" s="28">
+        <v>128</v>
+      </c>
+      <c r="H36" s="28">
+        <v>40</v>
+      </c>
+      <c r="I36" s="28">
+        <v>3.18</v>
+      </c>
+      <c r="J36" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="K36" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="28" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3443,7 +3490,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -3454,30 +3501,30 @@
     </row>
     <row r="2" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>32</v>
@@ -3505,7 +3552,7 @@
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>85</v>
@@ -3533,7 +3580,7 @@
     </row>
     <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>21</v>
@@ -3561,7 +3608,7 @@
     </row>
     <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>14</v>
@@ -3589,10 +3636,10 @@
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C7" s="33">
         <f>IFERROR(COUNTIFS('נתוני אימונים'!A:A,"*.12.2025*"),0)</f>
@@ -3617,7 +3664,7 @@
     </row>
     <row r="10" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>32</v>
@@ -3645,7 +3692,7 @@
     </row>
     <row r="11" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>85</v>
@@ -3673,7 +3720,7 @@
     </row>
     <row r="12" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>21</v>
@@ -3701,7 +3748,7 @@
     </row>
     <row r="13" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>14</v>
@@ -3729,10 +3776,10 @@
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C14" s="33">
         <f>IFERROR(COUNTIFS('נתוני אימונים'!A:A,"*.01.2026*"),0)</f>
@@ -3757,7 +3804,7 @@
     </row>
     <row r="17" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>32</v>
@@ -3785,7 +3832,7 @@
     </row>
     <row r="18" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>85</v>
@@ -3813,7 +3860,7 @@
     </row>
     <row r="19" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>21</v>
@@ -3841,7 +3888,7 @@
     </row>
     <row r="20" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>14</v>
@@ -3869,10 +3916,10 @@
     </row>
     <row r="21" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C21" s="33">
         <f>IFERROR(COUNTIFS('נתוני אימונים'!A:A,"*.02.2026*"),0)</f>
@@ -3897,7 +3944,7 @@
     </row>
     <row r="24" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>32</v>
@@ -3925,7 +3972,7 @@
     </row>
     <row r="25" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>85</v>
@@ -3953,7 +4000,7 @@
     </row>
     <row r="26" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>21</v>
@@ -3981,7 +4028,7 @@
     </row>
     <row r="27" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>14</v>
@@ -4009,10 +4056,10 @@
     </row>
     <row r="28" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>155</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>152</v>
       </c>
       <c r="C28" s="33">
         <f>IFERROR(COUNTIFS('נתוני אימונים'!A:A,"*.03.2026*"),0)</f>
@@ -4037,7 +4084,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>32</v>
@@ -4065,7 +4112,7 @@
     </row>
     <row r="32" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B32" s="36" t="s">
         <v>85</v>
@@ -4093,7 +4140,7 @@
     </row>
     <row r="33" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>21</v>
@@ -4121,7 +4168,7 @@
     </row>
     <row r="34" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>14</v>
@@ -4149,10 +4196,10 @@
     </row>
     <row r="35" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C35" s="33">
         <f>IFERROR(COUNTIFS('נתוני אימונים'!A:A,"*.04.2026*"),0)</f>
@@ -4182,7 +4229,7 @@
     <row r="40" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B41" t="s">
         <v>32</v>
@@ -4210,35 +4257,35 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B42" t="s">
         <v>85</v>
       </c>
       <c r="C42">
         <f>IFERROR(COUNTIFS('נתוני אימונים'!A:A,"*.05.2026*",'נתוני אימונים'!B:B,"אירובי ארוך"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D42" t="str">
+        <v>1</v>
+      </c>
+      <c r="D42">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.05.2026*",'נתוני אימונים'!B:B,"אירובי ארוך"),"")</f>
-        <v/>
-      </c>
-      <c r="E42" t="str">
+        <v>7.6</v>
+      </c>
+      <c r="E42">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!G:G,'נתוני אימונים'!A:A,"*.05.2026*",'נתוני אימונים'!B:B,"אירובי ארוך"),"")</f>
-        <v/>
-      </c>
-      <c r="F42" t="str">
+        <v>128</v>
+      </c>
+      <c r="F42">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!I:I,'נתוני אימונים'!A:A,"*.05.2026*",'נתוני אימונים'!B:B,"אירובי ארוך"),"")</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="G42">
         <f>IFERROR(SUMIFS('נתוני אימונים'!D:D,'נתוני אימונים'!A:A,"*.05.2026*",'נתוני אימונים'!B:B,"אירובי ארוך"),"")</f>
-        <v>0</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B43" t="s">
         <v>21</v>
@@ -4266,7 +4313,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -4294,14 +4341,14 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C45">
         <f>IFERROR(COUNTIFS('נתוני אימונים'!A:A,"*.05.2026*"),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.05.2026*"),"")</f>
@@ -4309,43 +4356,43 @@
       </c>
       <c r="E45">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!G:G,'נתוני אימונים'!A:A,"*.05.2026*"),"")</f>
-        <v>135</v>
+        <v>131.5</v>
       </c>
       <c r="F45">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!I:I,'נתוני אימונים'!A:A,"*.05.2026*"),"")</f>
-        <v>3.21</v>
+        <v>3.1950000000000003</v>
       </c>
       <c r="G45">
         <f>IFERROR(SUMIFS('נתוני אימונים'!D:D,'נתוני אימונים'!A:A,"*.05.2026*"),"")</f>
-        <v>9.4700000000000006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>20.64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -4374,7 +4421,7 @@
       </c>
       <c r="G48" s="19">
         <f>IFERROR(COUNTIF('נתוני אימונים'!B:B,"אירובי")/COUNTA('נתוני אימונים'!A3:A999),"")</f>
-        <v>0.45454545454545453</v>
+        <v>0.44117647058823528</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -4383,27 +4430,27 @@
       </c>
       <c r="B49" s="12">
         <f>IFERROR(COUNTIF('נתוני אימונים'!B:B,"אירובי ארוך"),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" s="30">
         <f>IFERROR(AVERAGEIF('נתוני אימונים'!B:B,"אירובי ארוך",'נתוני אימונים'!F:F),"")</f>
-        <v>7.9499999999999993</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="D49" s="12">
         <f>IFERROR(AVERAGEIF('נתוני אימונים'!B:B,"אירובי ארוך",'נתוני אימונים'!G:G),"")</f>
-        <v>135.5</v>
+        <v>133</v>
       </c>
       <c r="E49" s="30">
         <f>IFERROR(AVERAGEIF('נתוני אימונים'!B:B,"אירובי ארוך",'נתוני אימונים'!I:I),"")</f>
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="F49" s="12">
         <f>IFERROR(SUMIF('נתוני אימונים'!B:B,"אירובי ארוך",'נתוני אימונים'!D:D),"")</f>
-        <v>33.619999999999997</v>
+        <v>44.79</v>
       </c>
       <c r="G49" s="20">
         <f>IFERROR(COUNTIF('נתוני אימונים'!B:B,"אירובי ארוך")/COUNTA('נתוני אימונים'!A3:A999),"")</f>
-        <v>6.0606060606060608E-2</v>
+        <v>8.8235294117647065E-2</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -4432,7 +4479,7 @@
       </c>
       <c r="G50" s="21">
         <f>IFERROR(COUNTIF('נתוני אימונים'!B:B,"טמפו")/COUNTA('נתוני אימונים'!A3:A999),"")</f>
-        <v>0.33333333333333331</v>
+        <v>0.3235294117647059</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -4461,35 +4508,35 @@
       </c>
       <c r="G51" s="22">
         <f>IFERROR(COUNTIF('נתוני אימונים'!B:B,"ספרינטים")/COUNTA('נתוני אימונים'!A3:A999),"")</f>
-        <v>0.15151515151515152</v>
+        <v>0.14705882352941177</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B52" s="24">
         <f>COUNTA('נתוני אימונים'!A3:A999)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C52" s="35">
         <f>IFERROR(AVERAGE('נתוני אימונים'!F3:F999),"")</f>
-        <v>7.1303030303030299</v>
+        <v>7.144117647058823</v>
       </c>
       <c r="D52" s="24">
         <f>IFERROR(AVERAGE('נתוני אימונים'!G3:G999),"")</f>
-        <v>134.63636363636363</v>
+        <v>134.44117647058823</v>
       </c>
       <c r="E52" s="35">
         <f>IFERROR(AVERAGE('נתוני אימונים'!I3:I999),"")</f>
-        <v>3.1</v>
+        <v>3.1023529411764708</v>
       </c>
       <c r="F52" s="24">
         <f>IFERROR(SUM('נתוני אימונים'!D3:D999),"")</f>
-        <v>300.43000000000006</v>
+        <v>311.60000000000008</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4507,24 +4554,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B2">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.12.2025*"),0)</f>
@@ -4545,7 +4592,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B3">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.01.2026*"),0)</f>
@@ -4566,7 +4613,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B4">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.02.2026*"),0)</f>
@@ -4587,7 +4634,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B5">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.03.2026*"),0)</f>
@@ -4608,7 +4655,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B6">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.04.2026*"),0)</f>
@@ -4629,7 +4676,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B7">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!F:F,'נתוני אימונים'!A:A,"*.05.2026*"),0)</f>
@@ -4637,15 +4684,15 @@
       </c>
       <c r="C7">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!G:G,'נתוני אימונים'!A:A,"*.05.2026*"),0)</f>
-        <v>135</v>
+        <v>131.5</v>
       </c>
       <c r="D7">
         <f>IFERROR(AVERAGEIFS('נתוני אימונים'!I:I,'נתוני אימונים'!A:A,"*.05.2026*"),0)</f>
-        <v>3.21</v>
+        <v>3.1950000000000003</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>5.6296296296296296E-2</v>
+        <v>5.7794676806083647E-2</v>
       </c>
     </row>
   </sheetData>

--- a/ניתוח_אימוני_SUP_v5.xlsx
+++ b/ניתוח_אימוני_SUP_v5.xlsx
@@ -1460,7 +1460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" style="41" min="1" max="1"/>
@@ -3987,6 +3987,370 @@
       <c r="L49" s="28" t="inlineStr">
         <is>
           <t>59:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="inlineStr">
+        <is>
+          <t>אירובי</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
+        <is>
+          <t>ים</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>55:29</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G50" s="28" t="n">
+        <v>133</v>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
+        <is>
+          <t>43:48</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="inlineStr">
+        <is>
+          <t>0:01</t>
+        </is>
+      </c>
+      <c r="L50" s="28" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="inlineStr">
+        <is>
+          <t>אירובי</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>ים</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>1:17:13</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G51" s="28" t="n">
+        <v>138</v>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>57:32</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="L51" s="28" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>טמפו</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>ים</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>1:15:03</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G52" s="28" t="n">
+        <v>141</v>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>36:22</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>28:59</t>
+        </is>
+      </c>
+      <c r="L52" s="28" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>אירובי ארוך</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>ים</t>
+        </is>
+      </c>
+      <c r="D53" s="28" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>1:54:31</t>
+        </is>
+      </c>
+      <c r="F53" s="28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G53" s="28" t="n">
+        <v>137</v>
+      </c>
+      <c r="H53" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>1:47:47</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>0:13</t>
+        </is>
+      </c>
+      <c r="L53" s="28" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>22.06.2026</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>טמפו</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="inlineStr">
+        <is>
+          <t>ים</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E54" s="28" t="inlineStr">
+        <is>
+          <t>1:15:38</t>
+        </is>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G54" s="28" t="n">
+        <v>139</v>
+      </c>
+      <c r="H54" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
+        <is>
+          <t>41:25</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="L54" s="28" t="inlineStr">
+        <is>
+          <t>0:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>טמפו</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>ים</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="E55" s="28" t="inlineStr">
+        <is>
+          <t>1:15:22</t>
+        </is>
+      </c>
+      <c r="F55" s="28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G55" s="28" t="n">
+        <v>144</v>
+      </c>
+      <c r="H55" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="I55" s="28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>43:49</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>30:00</t>
+        </is>
+      </c>
+      <c r="L55" s="28" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>אירובי</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>ים</t>
+        </is>
+      </c>
+      <c r="D56" s="28" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>1:12:20</t>
+        </is>
+      </c>
+      <c r="F56" s="28" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G56" s="28" t="n">
+        <v>135</v>
+      </c>
+      <c r="H56" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="I56" s="28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
+        <is>
+          <t>1:02:40</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>0:13</t>
+        </is>
+      </c>
+      <c r="L56" s="28" t="inlineStr">
+        <is>
+          <t>0:00</t>
         </is>
       </c>
     </row>
